--- a/tasks/finalpool/yt-fireship-scholarly-excel-notion/groundtruth_workspace/Tech_Research_Map.xlsx
+++ b/tasks/finalpool/yt-fireship-scholarly-excel-notion/groundtruth_workspace/Tech_Research_Map.xlsx
@@ -726,418 +726,318 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F111"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1"/>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101">
-      <c r="A101" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Tech_Topic</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Paper_Title</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>First_Author</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Citations</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Abstract_Snippet</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>AI and Large Language Models</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>DeepSeek R1: Incentivizing Reasoning Capability in LLMs via Reinforcement Learning</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>DeepSeek Team</t>
         </is>
       </c>
-      <c r="D102" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E102" t="n">
+      <c r="D2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E2" t="n">
         <v>1204</v>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>We introduce DeepSeek R1, a large language model trained using reinforcement learning to improve reasoning capability.</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>AI and Large Language Models</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Large Language Models for Automated Reasoning: A Comprehensive Survey</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Yann Lecun</t>
         </is>
       </c>
-      <c r="D103" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E103" t="n">
+      <c r="D3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E3" t="n">
         <v>892</v>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>We survey large language models (LLMs) with focus on automated reasoning capabilities.</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Hardware and Computing</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Next-Generation Quantum-Classical Hybrid Computing Architectures</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>John Preskill</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E4" t="n">
+        <v>423</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>We examine emerging quantum-classical hybrid computing architectures that combine quantum processing units with classical CPUs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Hardware and Computing</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Energy-Efficient Neural Processing Units: Design and Benchmarking</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bill Dally</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E5" t="n">
+        <v>267</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>This paper presents design principles and benchmarking results for energy-efficient neural processing units.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Linux and Systems</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Performance Analysis of Linux Kernel Scheduler Algorithms in Cloud Environments</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Linus Torvalds</t>
         </is>
       </c>
-      <c r="D104" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E104" t="n">
+      <c r="D6" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E6" t="n">
         <v>245</v>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>This paper analyzes the performance of Linux kernel scheduler algorithms across various cloud computing workloads.</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Linux and Systems</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>eBPF-Based Observability Tools for Linux System Performance Monitoring</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Brendan Gregg</t>
         </is>
       </c>
-      <c r="D105" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E105" t="n">
+      <c r="D7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E7" t="n">
         <v>178</v>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Extended Berkeley Packet Filter (eBPF) has revolutionized Linux observability.</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Supply Chain Security Vulnerabilities in Open Source Software: A Systematic Review</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ross Anderson</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E8" t="n">
+        <v>334</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>This systematic review examines supply chain security vulnerabilities in open source software ecosystems.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Internet Archive Attacks: Analysis of Large-Scale DDoS and Data Breach Incidents</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Bruce Schneier</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E9" t="n">
+        <v>156</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>We analyze the 2024 attacks on digital preservation infrastructure including DDoS attacks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Software Engineering</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Automated Detection and Classification of Software Bugs Using Deep Learning</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Martin Fowler</t>
         </is>
       </c>
-      <c r="D106" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E106" t="n">
+      <c r="D10" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E10" t="n">
         <v>312</v>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>We present a deep learning approach for automated detection and classification of software bugs.</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Software Engineering</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Root Cause Analysis in Distributed Systems: Patterns from Large-Scale Incidents</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Charity Majors</t>
         </is>
       </c>
-      <c r="D107" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E107" t="n">
+      <c r="D11" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E11" t="n">
         <v>189</v>
       </c>
-      <c r="F107" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>This paper analyzes root cause patterns from thousands of production incidents in distributed systems.</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Hardware and Computing</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Next-Generation Quantum-Classical Hybrid Computing Architectures</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>John Preskill</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E108" t="n">
-        <v>423</v>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>We examine emerging quantum-classical hybrid computing architectures that combine quantum processing units with classical CPUs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Hardware and Computing</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Energy-Efficient Neural Processing Units: Design and Benchmarking</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Bill Dally</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E109" t="n">
-        <v>267</v>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>This paper presents design principles and benchmarking results for energy-efficient neural processing units.</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Supply Chain Security Vulnerabilities in Open Source Software: A Systematic Review</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Ross Anderson</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E110" t="n">
-        <v>334</v>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>This systematic review examines supply chain security vulnerabilities in open source software ecosystems.</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Internet Archive Attacks: Analysis of Large-Scale DDoS and Data Breach Incidents</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Bruce Schneier</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E111" t="n">
-        <v>156</v>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>We analyze the 2024 attacks on digital preservation infrastructure including DDoS attacks.</t>
         </is>
       </c>
     </row>
